--- a/hasil/Non-CLAHE/Run8/hasil_metrik.xlsx
+++ b/hasil/Non-CLAHE/Run8/hasil_metrik.xlsx
@@ -485,25 +485,25 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="H2" t="n">
         <v>0.9333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.8749999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
         <v>0.8222222222222222</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.7142857142857142</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="G4" t="n">
-        <v>0.875</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.8666666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -639,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/hasil/Non-CLAHE/Run8/hasil_metrik.xlsx
+++ b/hasil/Non-CLAHE/Run8/hasil_metrik.xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9111111111111111</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.9333333333333333</v>
-      </c>
       <c r="I2" t="n">
-        <v>0.8749999999999999</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7142857142857142</v>
+        <v>0.8148148148148148</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.875</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9032258064516129</v>
       </c>
     </row>
     <row r="6">
@@ -577,7 +577,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="9">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -639,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
